--- a/LineClass/decoy_mc_summary.xlsx
+++ b/LineClass/decoy_mc_summary.xlsx
@@ -498,46 +498,46 @@
         <v>-11.3</v>
       </c>
       <c r="B2" t="n">
-        <v>5156</v>
+        <v>3300</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>691</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>137</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1593</v>
+        <v>0.1875</v>
       </c>
       <c r="N2" t="n">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="3">
@@ -545,43 +545,43 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>5159</v>
+        <v>3298</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D3" t="n">
-        <v>712</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>192</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1945</v>
+        <v>0.1797</v>
       </c>
       <c r="N3" t="n">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
         <v>0.06</v>
@@ -592,43 +592,43 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>5163</v>
+        <v>3296</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="D4" t="n">
-        <v>683</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>192</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
-        <v>171</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1337</v>
+        <v>0.2127</v>
       </c>
       <c r="N4" t="n">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
         <v>0.07000000000000001</v>
@@ -639,43 +639,43 @@
         <v>-6.9</v>
       </c>
       <c r="B5" t="n">
-        <v>5152</v>
+        <v>3295</v>
       </c>
       <c r="C5" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="D5" t="n">
-        <v>728</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1566</v>
+        <v>0.3139</v>
       </c>
       <c r="N5" t="n">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
         <v>0.07000000000000001</v>
@@ -686,46 +686,46 @@
         <v>6.9</v>
       </c>
       <c r="B6" t="n">
-        <v>5136</v>
+        <v>3303</v>
       </c>
       <c r="C6" t="n">
-        <v>-19</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>695</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>166</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1687</v>
+        <v>0.1167</v>
       </c>
       <c r="N6" t="n">
-        <v>165</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
@@ -733,46 +733,46 @@
         <v>8.300000000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>5138</v>
+        <v>3298</v>
       </c>
       <c r="C7" t="n">
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>48</v>
       </c>
       <c r="E7" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1987</v>
+        <v>0.1014</v>
       </c>
       <c r="N7" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -780,43 +780,43 @@
         <v>9.699999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>5147</v>
+        <v>3292</v>
       </c>
       <c r="C8" t="n">
         <v>-8</v>
       </c>
       <c r="D8" t="n">
-        <v>730</v>
+        <v>38</v>
       </c>
       <c r="E8" t="n">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>170</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1776</v>
+        <v>0.2055</v>
       </c>
       <c r="N8" t="n">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="O8" t="n">
         <v>0.06</v>
@@ -827,46 +827,46 @@
         <v>11.3</v>
       </c>
       <c r="B9" t="n">
-        <v>5163</v>
+        <v>3287</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>-13</v>
       </c>
       <c r="D9" t="n">
-        <v>733</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
-        <v>190</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1728</v>
+        <v>0.1431</v>
       </c>
       <c r="N9" t="n">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/LineClass/decoy_mc_summary.xlsx
+++ b/LineClass/decoy_mc_summary.xlsx
@@ -498,46 +498,46 @@
         <v>-11.3</v>
       </c>
       <c r="B2" t="n">
-        <v>3300</v>
+        <v>4846</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>422</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1875</v>
+        <v>0.3663</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3">
@@ -545,46 +545,46 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>3298</v>
+        <v>4843</v>
       </c>
       <c r="C3" t="n">
-        <v>-2</v>
+        <v>-51</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>421</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="G3" t="n">
+        <v>76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>47</v>
+      </c>
+      <c r="I3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>0.1797</v>
+        <v>0.3822</v>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="4">
@@ -592,46 +592,46 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>3296</v>
+        <v>4841</v>
       </c>
       <c r="C4" t="n">
-        <v>-4</v>
+        <v>-53</v>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>372</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2127</v>
+        <v>0.4161</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5">
@@ -639,46 +639,46 @@
         <v>-6.9</v>
       </c>
       <c r="B5" t="n">
-        <v>3295</v>
+        <v>4839</v>
       </c>
       <c r="C5" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>348</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3139</v>
+        <v>0.3298</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>157</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6">
@@ -686,46 +686,46 @@
         <v>6.9</v>
       </c>
       <c r="B6" t="n">
-        <v>3303</v>
+        <v>4823</v>
       </c>
       <c r="C6" t="n">
+        <v>-71</v>
+      </c>
+      <c r="D6" t="n">
+        <v>390</v>
+      </c>
+      <c r="E6" t="n">
+        <v>150</v>
+      </c>
+      <c r="F6" t="n">
+        <v>117</v>
+      </c>
+      <c r="G6" t="n">
+        <v>82</v>
+      </c>
+      <c r="H6" t="n">
+        <v>44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E6" t="n">
-        <v>28</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.1167</v>
+        <v>0.3868</v>
       </c>
       <c r="N6" t="n">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="7">
@@ -733,46 +733,46 @@
         <v>8.300000000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>3298</v>
+        <v>4845</v>
       </c>
       <c r="C7" t="n">
-        <v>-2</v>
+        <v>-49</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>391</v>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1014</v>
+        <v>0.3443</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -780,46 +780,46 @@
         <v>9.699999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>3292</v>
+        <v>4822</v>
       </c>
       <c r="C8" t="n">
-        <v>-8</v>
+        <v>-72</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>386</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="F8" t="n">
+        <v>117</v>
+      </c>
+      <c r="G8" t="n">
+        <v>75</v>
+      </c>
+      <c r="H8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I8" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>0.2055</v>
+        <v>0.3916</v>
       </c>
       <c r="N8" t="n">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9">
@@ -827,46 +827,46 @@
         <v>11.3</v>
       </c>
       <c r="B9" t="n">
-        <v>3287</v>
+        <v>4831</v>
       </c>
       <c r="C9" t="n">
-        <v>-13</v>
+        <v>-63</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>397</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1431</v>
+        <v>0.3448</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>

--- a/LineClass/decoy_mc_summary.xlsx
+++ b/LineClass/decoy_mc_summary.xlsx
@@ -498,46 +498,46 @@
         <v>-11.3</v>
       </c>
       <c r="B2" t="n">
-        <v>4846</v>
+        <v>4840</v>
       </c>
       <c r="C2" t="n">
-        <v>-48</v>
+        <v>-51</v>
       </c>
       <c r="D2" t="n">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I2" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3663</v>
+        <v>0.4362</v>
       </c>
       <c r="N2" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="O2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3">
@@ -545,46 +545,46 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>4843</v>
+        <v>4830</v>
       </c>
       <c r="C3" t="n">
-        <v>-51</v>
+        <v>-61</v>
       </c>
       <c r="D3" t="n">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="E3" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F3" t="n">
         <v>118</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3822</v>
+        <v>0.4649</v>
       </c>
       <c r="N3" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="O3" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="4">
@@ -592,46 +592,46 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>4841</v>
+        <v>4857</v>
       </c>
       <c r="C4" t="n">
-        <v>-53</v>
+        <v>-34</v>
       </c>
       <c r="D4" t="n">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="E4" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F4" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G4" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4161</v>
+        <v>0.3649</v>
       </c>
       <c r="N4" t="n">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="O4" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -639,31 +639,31 @@
         <v>-6.9</v>
       </c>
       <c r="B5" t="n">
-        <v>4839</v>
+        <v>4843</v>
       </c>
       <c r="C5" t="n">
-        <v>-55</v>
+        <v>-48</v>
       </c>
       <c r="D5" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G5" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H5" t="n">
         <v>42</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -672,13 +672,13 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3298</v>
+        <v>0.361</v>
       </c>
       <c r="N5" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="6">
@@ -686,46 +686,46 @@
         <v>6.9</v>
       </c>
       <c r="B6" t="n">
-        <v>4823</v>
+        <v>4839</v>
       </c>
       <c r="C6" t="n">
-        <v>-71</v>
+        <v>-52</v>
       </c>
       <c r="D6" t="n">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="E6" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F6" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H6" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3868</v>
+        <v>0.3744</v>
       </c>
       <c r="N6" t="n">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="O6" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="7">
@@ -733,46 +733,46 @@
         <v>8.300000000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>4845</v>
+        <v>4862</v>
       </c>
       <c r="C7" t="n">
-        <v>-49</v>
+        <v>-29</v>
       </c>
       <c r="D7" t="n">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="E7" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
         <v>104</v>
       </c>
       <c r="G7" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3443</v>
+        <v>0.3458</v>
       </c>
       <c r="N7" t="n">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="8">
@@ -780,46 +780,46 @@
         <v>9.699999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>4822</v>
+        <v>4750</v>
       </c>
       <c r="C8" t="n">
-        <v>-72</v>
+        <v>-141</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E8" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J8" t="n">
         <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3916</v>
+        <v>0.4878</v>
       </c>
       <c r="N8" t="n">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="O8" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -827,46 +827,46 @@
         <v>11.3</v>
       </c>
       <c r="B9" t="n">
-        <v>4831</v>
+        <v>4832</v>
       </c>
       <c r="C9" t="n">
-        <v>-63</v>
+        <v>-59</v>
       </c>
       <c r="D9" t="n">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="E9" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F9" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G9" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3448</v>
+        <v>0.3729</v>
       </c>
       <c r="N9" t="n">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="O9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>

--- a/LineClass/decoy_mc_summary.xlsx
+++ b/LineClass/decoy_mc_summary.xlsx
@@ -498,46 +498,46 @@
         <v>-11.3</v>
       </c>
       <c r="B2" t="n">
-        <v>4840</v>
+        <v>4848</v>
       </c>
       <c r="C2" t="n">
-        <v>-51</v>
+        <v>-91</v>
       </c>
       <c r="D2" t="n">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4362</v>
+        <v>0.44</v>
       </c>
       <c r="N2" t="n">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="O2" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="3">
@@ -545,46 +545,46 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>4830</v>
+        <v>4854</v>
       </c>
       <c r="C3" t="n">
-        <v>-61</v>
+        <v>-85</v>
       </c>
       <c r="D3" t="n">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="E3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F3" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4649</v>
+        <v>0.3875</v>
       </c>
       <c r="N3" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O3" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="4">
@@ -592,46 +592,46 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="B4" t="n">
-        <v>4857</v>
+        <v>4859</v>
       </c>
       <c r="C4" t="n">
-        <v>-34</v>
+        <v>-80</v>
       </c>
       <c r="D4" t="n">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E4" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F4" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
         <v>35</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3649</v>
+        <v>0.3891</v>
       </c>
       <c r="N4" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="5">
@@ -639,46 +639,46 @@
         <v>-6.9</v>
       </c>
       <c r="B5" t="n">
-        <v>4843</v>
+        <v>4825</v>
       </c>
       <c r="C5" t="n">
-        <v>-48</v>
+        <v>-114</v>
       </c>
       <c r="D5" t="n">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E5" t="n">
         <v>140</v>
       </c>
       <c r="F5" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.361</v>
+        <v>0.3241</v>
       </c>
       <c r="N5" t="n">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="O5" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="6">
@@ -686,46 +686,46 @@
         <v>6.9</v>
       </c>
       <c r="B6" t="n">
-        <v>4839</v>
+        <v>4867</v>
       </c>
       <c r="C6" t="n">
-        <v>-52</v>
+        <v>-72</v>
       </c>
       <c r="D6" t="n">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="E6" t="n">
         <v>144</v>
       </c>
       <c r="F6" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3744</v>
+        <v>0.3696</v>
       </c>
       <c r="N6" t="n">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="O6" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="7">
@@ -733,46 +733,46 @@
         <v>8.300000000000001</v>
       </c>
       <c r="B7" t="n">
-        <v>4862</v>
+        <v>4874</v>
       </c>
       <c r="C7" t="n">
-        <v>-29</v>
+        <v>-65</v>
       </c>
       <c r="D7" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3458</v>
+        <v>0.346</v>
       </c>
       <c r="N7" t="n">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="O7" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="8">
@@ -780,46 +780,46 @@
         <v>9.699999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>4750</v>
+        <v>4775</v>
       </c>
       <c r="C8" t="n">
-        <v>-141</v>
+        <v>-164</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G8" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4878</v>
+        <v>0.5111</v>
       </c>
       <c r="N8" t="n">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9">
@@ -827,46 +827,46 @@
         <v>11.3</v>
       </c>
       <c r="B9" t="n">
-        <v>4832</v>
+        <v>4828</v>
       </c>
       <c r="C9" t="n">
-        <v>-59</v>
+        <v>-111</v>
       </c>
       <c r="D9" t="n">
         <v>368</v>
       </c>
       <c r="E9" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G9" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
         <v>40</v>
       </c>
       <c r="I9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3729</v>
+        <v>0.4225</v>
       </c>
       <c r="N9" t="n">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
